--- a/data/trans_camb/P16A15-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P16A15-Provincia-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,82; 9,51</t>
+          <t>1,04; 9,83</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,41; 7,07</t>
+          <t>-0,81; 6,38</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,43; 12,72</t>
+          <t>4,25; 12,49</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,26; 6,94</t>
+          <t>-3,15; 6,87</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-2,95; 6,77</t>
+          <t>-3,44; 6,85</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,79; 9,5</t>
+          <t>0,83; 9,63</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,53; 7,14</t>
+          <t>0,51; 7,18</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-0,37; 5,59</t>
+          <t>-0,61; 5,34</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3,82; 9,76</t>
+          <t>3,66; 9,89</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>8,1; 381,98</t>
+          <t>10,61; 385,2</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-11,25; 318,82</t>
+          <t>-15,96; 264,1</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>72,85; 509,97</t>
+          <t>67,95; 510,74</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-32,55; 117,13</t>
+          <t>-33,12; 126,96</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-29,84; 124,46</t>
+          <t>-33,48; 128,35</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,09; 184,1</t>
+          <t>5,98; 171,71</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,53; 161,66</t>
+          <t>5,18; 161,45</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-5,33; 128,33</t>
+          <t>-9,7; 115,36</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>52,3; 216,54</t>
+          <t>45,05; 236,5</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,08; 9,93</t>
+          <t>2,19; 9,88</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,34; 7,27</t>
+          <t>0,17; 7,15</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,8; 6,42</t>
+          <t>-0,07; 6,7</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,95; 11,07</t>
+          <t>3,34; 11,19</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,68; 9,17</t>
+          <t>1,69; 8,87</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,01; 7,96</t>
+          <t>1,34; 7,91</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,87; 9,24</t>
+          <t>3,86; 9,27</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,88; 7,31</t>
+          <t>1,92; 7,23</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,19; 6,28</t>
+          <t>1,15; 5,97</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>24,22; 200,84</t>
+          <t>26,03; 198,62</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,62; 143,63</t>
+          <t>1,86; 143,91</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-12,02; 121,51</t>
+          <t>-2,77; 138,28</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>32,04; 180,02</t>
+          <t>32,88; 173,34</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>17,23; 154,3</t>
+          <t>16,33; 144,21</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>9,57; 134,7</t>
+          <t>14,29; 133,44</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>44,95; 156,19</t>
+          <t>42,49; 157,2</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>22,13; 121,08</t>
+          <t>22,37; 120,56</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>14,22; 103,83</t>
+          <t>13,55; 105,25</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,04; 7,16</t>
+          <t>-1,93; 6,79</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,28; 8,49</t>
+          <t>-0,59; 8,66</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,82; 11,96</t>
+          <t>2,6; 11,4</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,59; 8,49</t>
+          <t>-0,76; 8,72</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,04; 10,18</t>
+          <t>0,29; 9,95</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,2; 11,57</t>
+          <t>2,85; 11,31</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,09; 6,68</t>
+          <t>0,04; 6,46</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,49; 8,3</t>
+          <t>1,38; 7,81</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>4,09; 10,43</t>
+          <t>4,18; 10,38</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-21,8; 126,83</t>
+          <t>-20,99; 115,11</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-2,78; 154,01</t>
+          <t>-7,74; 144,8</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>27,93; 212,28</t>
+          <t>22,55; 188,67</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-7,66; 136,57</t>
+          <t>-10,48; 139,3</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-1,02; 159,49</t>
+          <t>0,48; 158,95</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>26,67; 195,19</t>
+          <t>24,15; 189,27</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 98,77</t>
+          <t>-0,15; 94,75</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>14,7; 126,4</t>
+          <t>14,31; 115,74</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>42,22; 164,42</t>
+          <t>44,99; 162,68</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,06; 10,17</t>
+          <t>1,97; 10,4</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,59; 10,03</t>
+          <t>2,51; 10,28</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3,57; 11,75</t>
+          <t>3,75; 12,2</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4,45; 12,5</t>
+          <t>4,49; 12,03</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>4,25; 12,72</t>
+          <t>4,21; 12,58</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,54; 9,24</t>
+          <t>0,34; 9,85</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,19; 10,0</t>
+          <t>4,41; 10,19</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>4,32; 9,87</t>
+          <t>4,16; 9,84</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3,02; 9,23</t>
+          <t>2,6; 9,25</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>28,38; 312,2</t>
+          <t>28,39; 331,56</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>40,2; 346,75</t>
+          <t>36,78; 321,57</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>50,34; 389,09</t>
+          <t>54,18; 373,6</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>60,42; 352,69</t>
+          <t>59,14; 323,59</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>54,04; 333,52</t>
+          <t>56,22; 339,88</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>9,79; 235,87</t>
+          <t>8,06; 259,54</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>70,22; 267,23</t>
+          <t>66,73; 253,19</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>69,89; 255,56</t>
+          <t>62,6; 241,22</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>54,71; 238,75</t>
+          <t>45,77; 231,04</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,41; 12,87</t>
+          <t>0,15; 12,77</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,81; 11,09</t>
+          <t>-1,34; 10,07</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3,22; 14,25</t>
+          <t>3,02; 14,49</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>6,66; 19,65</t>
+          <t>7,28; 19,46</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1,9; 12,88</t>
+          <t>2,35; 13,14</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>11,14; 20,5</t>
+          <t>11,2; 20,43</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>5,12; 13,76</t>
+          <t>5,75; 14,25</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>2,25; 10,26</t>
+          <t>2,23; 10,47</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>9,06; 16,35</t>
+          <t>9,32; 16,71</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>0,52; 265,83</t>
+          <t>-1,18; 261,5</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-12,22; 239,39</t>
+          <t>-15,72; 216,78</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>26,45; 314,59</t>
+          <t>24,15; 350,05</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>71,32; 534,18</t>
+          <t>78,41; 554,23</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>17,42; 335,06</t>
+          <t>23,09; 374,11</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>125,12; 600,69</t>
+          <t>112,33; 582,52</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>58,99; 276,36</t>
+          <t>60,33; 278,42</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>26,26; 198,18</t>
+          <t>23,44; 207,32</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>101,25; 352,27</t>
+          <t>102,03; 345,91</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>3,51; 12,93</t>
+          <t>3,61; 13,33</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-0,7; 7,94</t>
+          <t>-0,04; 8,53</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>11,19; 20,59</t>
+          <t>11,32; 20,83</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-3,27; 7,53</t>
+          <t>-3,6; 6,9</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-7,04; 2,92</t>
+          <t>-7,56; 2,93</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,01; 10,8</t>
+          <t>1,0; 10,26</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,38; 8,5</t>
+          <t>1,28; 8,85</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-2,73; 4,13</t>
+          <t>-2,55; 4,22</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>7,17; 13,8</t>
+          <t>7,39; 14,11</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>39,05; 408,08</t>
+          <t>39,69; 393,19</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-15,09; 236,33</t>
+          <t>-10,16; 264,83</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>148,99; 659,04</t>
+          <t>147,09; 698,07</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-23,21; 86,58</t>
+          <t>-24,76; 82,76</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-50,34; 35,93</t>
+          <t>-52,1; 37,01</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>5,64; 125,48</t>
+          <t>4,26; 116,64</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>13,94; 129,54</t>
+          <t>11,3; 134,96</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-27,32; 60,64</t>
+          <t>-26,77; 66,33</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>74,4; 220,96</t>
+          <t>71,38; 219,93</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>1,78; 7,97</t>
+          <t>1,84; 8,17</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-0,8; 4,92</t>
+          <t>-0,53; 5,34</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1,94; 7,92</t>
+          <t>1,57; 7,72</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-0,05; 6,67</t>
+          <t>-0,38; 6,29</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-3,1; 3,04</t>
+          <t>-3,07; 3,03</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>5,52; 57,52</t>
+          <t>5,35; 59,85</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>1,74; 6,42</t>
+          <t>1,76; 6,37</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-1,05; 3,24</t>
+          <t>-0,79; 3,5</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>5,03; 47,18</t>
+          <t>5,04; 45,47</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>22,76; 173,16</t>
+          <t>25,27; 194,45</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-12,96; 105,41</t>
+          <t>-9,01; 120,71</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>25,97; 181,67</t>
+          <t>21,62; 181,0</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-0,8; 106,1</t>
+          <t>-4,46; 98,78</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-32,67; 50,6</t>
+          <t>-32,74; 47,86</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>67,05; 1223,71</t>
+          <t>64,86; 1063,28</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>22,59; 109,4</t>
+          <t>22,44; 111,18</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-13,92; 55,51</t>
+          <t>-10,49; 61,25</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>71,96; 795,43</t>
+          <t>68,95; 796,61</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-1,58; 3,59</t>
+          <t>-1,23; 3,99</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>0,34; 5,59</t>
+          <t>0,18; 5,43</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-2,77; 5,49</t>
+          <t>-3,51; 5,61</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-1,36; 4,49</t>
+          <t>-1,63; 4,25</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-0,9; 5,59</t>
+          <t>-0,97; 5,45</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>0,53; 6,26</t>
+          <t>0,46; 6,14</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-0,49; 3,11</t>
+          <t>-0,7; 3,4</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>0,83; 4,77</t>
+          <t>0,49; 4,73</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-2,39; 4,96</t>
+          <t>-2,32; 4,63</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-21,95; 76,58</t>
+          <t>-17,69; 83,94</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>4,66; 127,59</t>
+          <t>2,45; 115,56</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-43,42; 105,17</t>
+          <t>-45,87; 105,18</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-13,74; 64,18</t>
+          <t>-16,02; 56,47</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-8,64; 75,88</t>
+          <t>-9,25; 75,29</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>4,87; 88,4</t>
+          <t>3,59; 85,68</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-7,1; 47,31</t>
+          <t>-9,44; 52,69</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>8,99; 74,71</t>
+          <t>6,24; 73,87</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-22,01; 72,89</t>
+          <t>-23,73; 68,09</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>3,06; 5,76</t>
+          <t>3,22; 5,82</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>2,3; 4,85</t>
+          <t>2,31; 4,95</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>3,37; 7,25</t>
+          <t>2,3; 7,16</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>2,82; 5,75</t>
+          <t>2,93; 5,9</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>1,64; 4,57</t>
+          <t>1,68; 4,5</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>5,5; 26,72</t>
+          <t>5,36; 23,95</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>3,45; 5,45</t>
+          <t>3,34; 5,37</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>2,36; 4,39</t>
+          <t>2,41; 4,38</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>5,37; 17,71</t>
+          <t>5,29; 17,69</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>47,88; 110,72</t>
+          <t>50,08; 111,49</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>36,33; 92,83</t>
+          <t>35,68; 95,1</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>56,76; 137,98</t>
+          <t>41,41; 133,74</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>32,37; 78,8</t>
+          <t>34,92; 82,3</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>19,12; 62,36</t>
+          <t>19,17; 62,35</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>68,62; 347,52</t>
+          <t>65,32; 308,96</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>46,58; 83,89</t>
+          <t>46,5; 84,27</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>31,85; 67,24</t>
+          <t>33,25; 68,66</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>76,44; 274,75</t>
+          <t>76,77; 271,6</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P16A15-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P16A15-Provincia-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8,35</t>
+          <t>8,16</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,37</t>
+          <t>4,78</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>6,89</t>
+          <t>6,51</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,04; 9,83</t>
+          <t>0,55; 9,19</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,81; 6,38</t>
+          <t>-0,41; 6,66</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,25; 12,49</t>
+          <t>4,14; 12,38</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,15; 6,87</t>
+          <t>-2,95; 6,97</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-3,44; 6,85</t>
+          <t>-3,34; 7,19</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,83; 9,63</t>
+          <t>-0,09; 8,72</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,51; 7,18</t>
+          <t>0,04; 6,72</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-0,61; 5,34</t>
+          <t>-0,61; 5,45</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3,66; 9,89</t>
+          <t>3,6; 9,6</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>212,17%</t>
+          <t>207,33%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>68,68%</t>
+          <t>61,14%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>118,1%</t>
+          <t>111,68%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>10,61; 385,2</t>
+          <t>7,15; 355,68</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-15,96; 264,1</t>
+          <t>-9,35; 278,0</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>67,95; 510,74</t>
+          <t>61,14; 503,33</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-33,12; 126,96</t>
+          <t>-29,61; 125,35</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-33,48; 128,35</t>
+          <t>-33,15; 130,45</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,98; 171,71</t>
+          <t>-2,36; 165,85</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,18; 161,45</t>
+          <t>-0,56; 161,24</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-9,7; 115,36</t>
+          <t>-9,7; 123,2</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>45,05; 236,5</t>
+          <t>44,07; 227,87</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2,91</t>
+          <t>3,01</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>4,42</t>
+          <t>4,28</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,19; 9,88</t>
+          <t>1,8; 10,32</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,17; 7,15</t>
+          <t>0,45; 7,19</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,07; 6,7</t>
+          <t>-0,38; 6,37</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,34; 11,19</t>
+          <t>3,23; 11,42</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,69; 8,87</t>
+          <t>1,31; 9,02</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,34; 7,91</t>
+          <t>0,46; 7,16</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,86; 9,27</t>
+          <t>4,15; 9,53</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,92; 7,23</t>
+          <t>2,04; 7,17</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,15; 5,97</t>
+          <t>1,18; 6,03</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>44,67%</t>
+          <t>46,17%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>57,6%</t>
+          <t>55,7%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>51,46%</t>
+          <t>51,44%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>26,03; 198,62</t>
+          <t>21,76; 201,54</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,86; 143,91</t>
+          <t>5,59; 146,74</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-2,77; 138,28</t>
+          <t>-5,12; 127,17</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>32,88; 173,34</t>
+          <t>31,33; 176,34</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>16,33; 144,21</t>
+          <t>14,04; 150,47</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>14,29; 133,44</t>
+          <t>5,4; 121,3</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>42,49; 157,2</t>
+          <t>48,1; 151,3</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>22,37; 120,56</t>
+          <t>23,87; 119,38</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>13,55; 105,25</t>
+          <t>13,84; 103,23</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>7,2</t>
+          <t>6,98</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>7,42</t>
+          <t>7,41</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>7,32</t>
+          <t>7,22</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,93; 6,79</t>
+          <t>-1,7; 7,17</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,59; 8,66</t>
+          <t>-0,38; 8,72</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,6; 11,4</t>
+          <t>2,22; 11,5</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,76; 8,72</t>
+          <t>-0,61; 8,91</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,29; 9,95</t>
+          <t>0,14; 10,01</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,85; 11,31</t>
+          <t>3,03; 11,75</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,04; 6,46</t>
+          <t>0,04; 6,55</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,38; 7,81</t>
+          <t>1,27; 8,14</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>4,18; 10,38</t>
+          <t>4,09; 10,09</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>91,6%</t>
+          <t>88,85%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>90,11%</t>
+          <t>90,01%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>90,91%</t>
+          <t>89,63%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-20,99; 115,11</t>
+          <t>-16,78; 129,95</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-7,74; 144,8</t>
+          <t>-5,59; 151,12</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>22,55; 188,67</t>
+          <t>19,06; 198,55</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-10,48; 139,3</t>
+          <t>-7,7; 143,64</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,48; 158,95</t>
+          <t>-2,04; 157,19</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>24,15; 189,27</t>
+          <t>26,11; 202,57</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-0,15; 94,75</t>
+          <t>0,16; 97,6</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>14,31; 115,74</t>
+          <t>12,84; 120,17</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>44,99; 162,68</t>
+          <t>39,92; 154,53</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>7,37</t>
+          <t>6,73</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,64</t>
+          <t>7,85</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>6,38</t>
+          <t>7,34</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,97; 10,4</t>
+          <t>1,82; 10,42</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,51; 10,28</t>
+          <t>2,24; 9,8</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3,75; 12,2</t>
+          <t>2,81; 10,99</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4,49; 12,03</t>
+          <t>4,3; 12,39</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>4,21; 12,58</t>
+          <t>3,72; 12,38</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,34; 9,85</t>
+          <t>4,27; 11,3</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,41; 10,19</t>
+          <t>4,49; 10,24</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>4,16; 9,84</t>
+          <t>4,22; 10,04</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2,6; 9,25</t>
+          <t>4,95; 9,82</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>161,51%</t>
+          <t>147,62%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>109,89%</t>
+          <t>152,85%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>131,48%</t>
+          <t>151,2%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>28,39; 331,56</t>
+          <t>26,68; 306,53</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>36,78; 321,57</t>
+          <t>31,32; 313,94</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>54,18; 373,6</t>
+          <t>41,01; 331,86</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>59,14; 323,59</t>
+          <t>58,55; 326,57</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>56,22; 339,88</t>
+          <t>52,29; 345,37</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>8,06; 259,54</t>
+          <t>57,41; 328,31</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>66,73; 253,19</t>
+          <t>69,38; 264,95</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>62,6; 241,22</t>
+          <t>70,71; 261,94</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>45,77; 231,04</t>
+          <t>82,28; 257,07</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>9,04</t>
+          <t>7,98</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>16,17</t>
+          <t>15,16</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>12,83</t>
+          <t>11,72</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,15; 12,77</t>
+          <t>0,61; 12,61</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-1,34; 10,07</t>
+          <t>-0,93; 10,35</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3,02; 14,49</t>
+          <t>2,58; 13,72</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>7,28; 19,46</t>
+          <t>6,4; 19,2</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>2,35; 13,14</t>
+          <t>2,54; 13,53</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>11,2; 20,43</t>
+          <t>10,39; 19,77</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>5,75; 14,25</t>
+          <t>4,99; 13,99</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>2,23; 10,47</t>
+          <t>2,38; 10,26</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>9,32; 16,71</t>
+          <t>8,02; 15,12</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>123,66%</t>
+          <t>109,21%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>275,84%</t>
+          <t>258,75%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>195,04%</t>
+          <t>178,23%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-1,18; 261,5</t>
+          <t>-2,46; 249,25</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-15,72; 216,78</t>
+          <t>-13,52; 217,1</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>24,15; 350,05</t>
+          <t>20,05; 311,34</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>78,41; 554,23</t>
+          <t>72,92; 549,16</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>23,09; 374,11</t>
+          <t>27,39; 388,57</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>112,33; 582,52</t>
+          <t>108,95; 617,21</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>60,33; 278,42</t>
+          <t>58,25; 283,27</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>23,44; 207,32</t>
+          <t>25,41; 225,35</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>102,03; 345,91</t>
+          <t>82,95; 319,94</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>16,05</t>
+          <t>15,57</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>5,74</t>
+          <t>5,92</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>10,9</t>
+          <t>10,73</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>3,61; 13,33</t>
+          <t>3,78; 12,93</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-0,04; 8,53</t>
+          <t>-0,39; 8,18</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>11,32; 20,83</t>
+          <t>10,73; 20,86</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-3,6; 6,9</t>
+          <t>-3,34; 8,02</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-7,56; 2,93</t>
+          <t>-7,5; 3,25</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,0; 10,26</t>
+          <t>0,82; 10,66</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,28; 8,85</t>
+          <t>1,56; 8,84</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-2,55; 4,22</t>
+          <t>-2,37; 4,32</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>7,39; 14,11</t>
+          <t>7,5; 14,07</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>327,6%</t>
+          <t>317,81%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>51,47%</t>
+          <t>53,09%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>135,11%</t>
+          <t>132,93%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>39,69; 393,19</t>
+          <t>47,11; 420,95</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-10,16; 264,83</t>
+          <t>-8,34; 257,71</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>147,09; 698,07</t>
+          <t>131,48; 663,09</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-24,76; 82,76</t>
+          <t>-26,51; 92,13</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-52,1; 37,01</t>
+          <t>-53,59; 38,63</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>4,26; 116,64</t>
+          <t>5,81; 125,45</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>11,3; 134,96</t>
+          <t>14,49; 133,13</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-26,77; 66,33</t>
+          <t>-25,89; 68,87</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>71,38; 219,93</t>
+          <t>74,65; 221,32</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>4,93</t>
+          <t>5,23</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>27,13</t>
+          <t>6,53</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>17,86</t>
+          <t>5,92</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>1,84; 8,17</t>
+          <t>1,96; 8,2</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-0,53; 5,34</t>
+          <t>-0,5; 5,18</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1,57; 7,72</t>
+          <t>2,51; 8,6</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-0,38; 6,29</t>
+          <t>-0,25; 6,5</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-3,07; 3,03</t>
+          <t>-3,0; 3,19</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>5,35; 59,85</t>
+          <t>3,43; 9,47</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>1,76; 6,37</t>
+          <t>1,83; 6,23</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-0,79; 3,5</t>
+          <t>-0,87; 3,13</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>5,04; 45,47</t>
+          <t>3,81; 7,99</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>86,09%</t>
+          <t>91,39%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>350,41%</t>
+          <t>84,29%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>264,56%</t>
+          <t>87,65%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>25,27; 194,45</t>
+          <t>26,39; 182,77</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-9,01; 120,71</t>
+          <t>-7,74; 110,87</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>21,62; 181,0</t>
+          <t>35,32; 190,74</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-4,46; 98,78</t>
+          <t>-3,46; 100,06</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-32,74; 47,86</t>
+          <t>-33,15; 53,04</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>64,86; 1063,28</t>
+          <t>37,76; 154,21</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>22,44; 111,18</t>
+          <t>23,71; 110,09</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-10,49; 61,25</t>
+          <t>-11,46; 54,35</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>68,95; 796,61</t>
+          <t>47,92; 135,04</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>1,94</t>
+          <t>4,2</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>3,38</t>
+          <t>3,3</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>2,33</t>
+          <t>3,73</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-1,23; 3,99</t>
+          <t>-1,38; 3,67</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>0,18; 5,43</t>
+          <t>0,32; 5,73</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-3,51; 5,61</t>
+          <t>1,67; 6,79</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-1,63; 4,25</t>
+          <t>-1,91; 4,11</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-0,97; 5,45</t>
+          <t>-0,74; 5,57</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>0,46; 6,14</t>
+          <t>0,54; 6,09</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-0,7; 3,4</t>
+          <t>-0,56; 3,28</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>0,49; 4,73</t>
+          <t>0,59; 4,74</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-2,32; 4,63</t>
+          <t>1,98; 5,71</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>33,51%</t>
+          <t>72,49%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>38,7%</t>
+          <t>37,79%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>32,0%</t>
+          <t>51,09%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-17,69; 83,94</t>
+          <t>-22,4; 80,14</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>2,45; 115,56</t>
+          <t>4,68; 123,25</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-45,87; 105,18</t>
+          <t>22,83; 154,09</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-16,02; 56,47</t>
+          <t>-18,86; 56,59</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-9,25; 75,29</t>
+          <t>-7,63; 74,9</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>3,59; 85,68</t>
+          <t>4,22; 84,16</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-9,44; 52,69</t>
+          <t>-6,83; 52,1</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>6,24; 73,87</t>
+          <t>7,2; 73,68</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-23,73; 68,09</t>
+          <t>23,47; 93,74</t>
         </is>
       </c>
     </row>
@@ -2362,7 +2362,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>5,63</t>
+          <t>6,17</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>10,65</t>
+          <t>5,99</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>8,22</t>
+          <t>6,09</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>3,22; 5,82</t>
+          <t>3,18; 5,91</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>2,31; 4,95</t>
+          <t>2,29; 4,75</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>2,3; 7,16</t>
+          <t>4,9; 7,37</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>2,93; 5,9</t>
+          <t>2,86; 5,77</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>1,68; 4,5</t>
+          <t>1,64; 4,56</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>5,36; 23,95</t>
+          <t>4,74; 7,26</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>3,34; 5,37</t>
+          <t>3,52; 5,39</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>2,41; 4,38</t>
+          <t>2,32; 4,32</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>5,29; 17,69</t>
+          <t>5,07; 7,02</t>
         </is>
       </c>
     </row>
@@ -2468,7 +2468,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>96,67%</t>
+          <t>106,02%</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -2483,7 +2483,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>134,93%</t>
+          <t>75,91%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>119,62%</t>
+          <t>88,62%</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>50,08; 111,49</t>
+          <t>49,76; 112,69</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>35,68; 95,1</t>
+          <t>35,47; 90,41</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>41,41; 133,74</t>
+          <t>76,19; 143,26</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>34,92; 82,3</t>
+          <t>32,68; 80,25</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>19,17; 62,35</t>
+          <t>18,33; 62,5</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>65,32; 308,96</t>
+          <t>55,16; 104,48</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>46,5; 84,27</t>
+          <t>47,78; 84,04</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>33,25; 68,66</t>
+          <t>31,61; 66,92</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>76,77; 271,6</t>
+          <t>68,32; 109,89</t>
         </is>
       </c>
     </row>
